--- a/香港現在上映電影 2025-11-03.xlsx
+++ b/香港現在上映電影 2025-11-03.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="167">
   <si>
     <t>英文名稱</t>
   </si>
@@ -415,10 +415,10 @@
     <t>3108萬</t>
   </si>
   <si>
-    <t>9.091億</t>
-  </si>
-  <si>
-    <t>14.37億</t>
+    <t>10.09億</t>
+  </si>
+  <si>
+    <t>14.76億</t>
   </si>
   <si>
     <t>155.4萬</t>
@@ -427,6 +427,9 @@
     <t>7.801億</t>
   </si>
   <si>
+    <t>8625萬</t>
+  </si>
+  <si>
     <t>5.416億</t>
   </si>
   <si>
@@ -436,7 +439,7 @@
     <t>12.28億</t>
   </si>
   <si>
-    <t>6.993億</t>
+    <t>8.135億</t>
   </si>
   <si>
     <t>4.002億</t>
@@ -451,7 +454,7 @@
     <t>8392萬</t>
   </si>
   <si>
-    <t>2.486億</t>
+    <t>2.906億</t>
   </si>
   <si>
     <t>8003萬</t>
@@ -972,10 +975,10 @@
         <v>102</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G2" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>125</v>
@@ -1001,7 +1004,7 @@
         <v>103</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G3" s="1">
         <v>21</v>
@@ -1030,7 +1033,7 @@
         <v>104</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G4" s="1">
         <v>11</v>
@@ -1045,7 +1048,7 @@
         <v>127</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1065,7 +1068,7 @@
         <v>105</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G5" s="1">
         <v>59</v>
@@ -1100,13 +1103,13 @@
         <v>106</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G6" s="1">
         <v>137</v>
       </c>
       <c r="H6" s="1">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I6" s="1">
         <v>50</v>
@@ -1135,7 +1138,7 @@
         <v>107</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G7" s="1">
         <v>37</v>
@@ -1170,13 +1173,13 @@
         <v>108</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G8" s="1">
         <v>34</v>
       </c>
       <c r="H8" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I8" s="1">
         <v>50</v>
@@ -1185,7 +1188,7 @@
         <v>126</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1205,7 +1208,7 @@
         <v>109</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G9" s="1">
         <v>34</v>
@@ -1214,7 +1217,7 @@
         <v>125</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1234,7 +1237,7 @@
         <v>110</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G10" s="1">
         <v>26</v>
@@ -1263,7 +1266,7 @@
         <v>111</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G11" s="1">
         <v>401</v>
@@ -1298,7 +1301,7 @@
         <v>108</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G12" s="1">
         <v>22</v>
@@ -1333,7 +1336,7 @@
         <v>112</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G13" s="1">
         <v>138</v>
@@ -1368,7 +1371,7 @@
         <v>113</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G14" s="1">
         <v>11</v>
@@ -1397,22 +1400,22 @@
         <v>114</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G15" s="1">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H15" s="1">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I15" s="1">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>128</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1432,7 +1435,7 @@
         <v>115</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G16" s="1">
         <v>20</v>
@@ -1447,7 +1450,7 @@
         <v>127</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1467,7 +1470,7 @@
         <v>105</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G17" s="1">
         <v>357</v>
@@ -1482,7 +1485,7 @@
         <v>126</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1502,7 +1505,7 @@
         <v>116</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G18" s="1">
         <v>10</v>
@@ -1517,7 +1520,7 @@
         <v>125</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1537,7 +1540,7 @@
         <v>117</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G19" s="1">
         <v>170</v>
@@ -1552,7 +1555,7 @@
         <v>128</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1572,7 +1575,7 @@
         <v>118</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G20" s="1">
         <v>6</v>
@@ -1601,7 +1604,7 @@
         <v>106</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G21" s="1">
         <v>187</v>
@@ -1616,7 +1619,7 @@
         <v>125</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1636,7 +1639,7 @@
         <v>119</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G22" s="1">
         <v>17</v>
@@ -1668,7 +1671,7 @@
         <v>120</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G23" s="1">
         <v>184</v>
@@ -1683,7 +1686,7 @@
         <v>125</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1703,7 +1706,7 @@
         <v>121</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G24" s="1">
         <v>248</v>
@@ -1718,7 +1721,7 @@
         <v>126</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1738,7 +1741,7 @@
         <v>122</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G25" s="1">
         <v>6</v>
@@ -1753,7 +1756,7 @@
         <v>126</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1773,7 +1776,7 @@
         <v>123</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G26" s="1">
         <v>76</v>
@@ -1788,7 +1791,7 @@
         <v>125</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1808,7 +1811,7 @@
         <v>124</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G27" s="1">
         <v>10</v>
@@ -1817,7 +1820,7 @@
         <v>128</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
